--- a/data/data_total_departamentos.xlsx
+++ b/data/data_total_departamentos.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3176</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="4">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>925</v>
+        <v>593</v>
       </c>
     </row>
     <row r="5">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>334</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1123</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>178</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1094</v>
+        <v>821</v>
       </c>
     </row>
     <row r="10">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>616</v>
+        <v>487</v>
       </c>
     </row>
     <row r="12">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>101</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>147</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>134</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>340</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19">
@@ -1318,6 +1318,240 @@
       </c>
       <c r="C68" t="n">
         <v>854</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LORETO</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_total_departamentos.xlsx
+++ b/data/data_total_departamentos.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2467</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="4">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="5">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>821</v>
+        <v>892</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>487</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>187</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6030</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1106</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="22">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1207</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="25">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1105</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="27">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>545</v>
+        <v>560</v>
       </c>
     </row>
     <row r="28">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>538</v>
+        <v>550</v>
       </c>
     </row>
     <row r="29">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>211</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30">
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>608</v>
+        <v>632</v>
       </c>
     </row>
     <row r="32">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>763</v>
+        <v>815</v>
       </c>
     </row>
     <row r="36">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5947</v>
+        <v>6472</v>
       </c>
     </row>
     <row r="38">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1476</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="39">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1473</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="42">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1852</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="44">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>780</v>
+        <v>784</v>
       </c>
     </row>
     <row r="45">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>615</v>
+        <v>626</v>
       </c>
     </row>
     <row r="46">
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>218</v>
+        <v>244</v>
       </c>
     </row>
     <row r="47">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>502</v>
+        <v>517</v>
       </c>
     </row>
     <row r="49">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="51">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>805</v>
+        <v>866</v>
       </c>
     </row>
     <row r="53">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4404</v>
+        <v>4774</v>
       </c>
     </row>
     <row r="55">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>918</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="56">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>371</v>
+        <v>399</v>
       </c>
     </row>
     <row r="57">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1194</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="58">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>343</v>
+        <v>360</v>
       </c>
     </row>
     <row r="59">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1939</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="60">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>348</v>
+        <v>358</v>
       </c>
     </row>
     <row r="61">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>237</v>
+        <v>252</v>
       </c>
     </row>
     <row r="62">
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="63">
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>374</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="67">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>54</v>
+        <v>197</v>
       </c>
     </row>
     <row r="68">
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>854</v>
+        <v>924</v>
       </c>
     </row>
     <row r="69">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="70">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>709</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="71">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>332</v>
+        <v>943</v>
       </c>
     </row>
     <row r="72">
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>99</v>
+        <v>215</v>
       </c>
     </row>
     <row r="73">
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>690</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="74">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>43</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>273</v>
+        <v>701</v>
       </c>
     </row>
     <row r="76">
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>129</v>
+        <v>258</v>
       </c>
     </row>
     <row r="78">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="80">
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82">
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>70</v>
+        <v>355</v>
       </c>
     </row>
     <row r="83">
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>48</v>
+        <v>101</v>
       </c>
     </row>
     <row r="84">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>153</v>
+        <v>539</v>
       </c>
     </row>
     <row r="85">
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86">
@@ -1547,11 +1547,128 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>MOQUEGUA</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="C93" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_total_departamentos.xlsx
+++ b/data/data_total_departamentos.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2617</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="4">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>596</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>892</v>
+        <v>775</v>
       </c>
     </row>
     <row r="10">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>510</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>268</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>206</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6251</v>
+        <v>4393</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1148</v>
+        <v>953</v>
       </c>
     </row>
     <row r="22">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1235</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="25">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1161</v>
+        <v>995</v>
       </c>
     </row>
     <row r="27">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="28">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>550</v>
+        <v>357</v>
       </c>
     </row>
     <row r="29">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>288</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30">
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>632</v>
+        <v>507</v>
       </c>
     </row>
     <row r="32">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>815</v>
+        <v>504</v>
       </c>
     </row>
     <row r="36">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6472</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="38">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1645</v>
+        <v>852</v>
       </c>
     </row>
     <row r="39">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>454</v>
+        <v>311</v>
       </c>
     </row>
     <row r="40">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1500</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="42">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>289</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1895</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="44">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>784</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>626</v>
+        <v>285</v>
       </c>
     </row>
     <row r="46">
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>244</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>105</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>517</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>293</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51">
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>149</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>866</v>
+        <v>482</v>
       </c>
     </row>
     <row r="53">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4774</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1364</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>399</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1612</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>360</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2105</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>358</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>252</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62">
@@ -1235,11 +1235,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>114</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
@@ -1261,11 +1261,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>415</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -1274,401 +1274,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>292</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46096</v>
+        <v>46097</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>AMAZONAS</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>1464</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>1732</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>HUANCAVELICA</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>LORETO</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>MOQUEGUA</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>PASCO</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>HUANCAVELICA</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>MOQUEGUA</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>PASCO</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_total_departamentos.xlsx
+++ b/data/data_total_departamentos.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1906</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="4">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>539</v>
+        <v>596</v>
       </c>
     </row>
     <row r="5">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>775</v>
+        <v>895</v>
       </c>
     </row>
     <row r="10">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>69</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>308</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>215</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>148</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4393</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>953</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="22">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="23">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1204</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="25">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>995</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="27">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>440</v>
+        <v>560</v>
       </c>
     </row>
     <row r="28">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>357</v>
+        <v>550</v>
       </c>
     </row>
     <row r="29">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>166</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30">
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>507</v>
+        <v>633</v>
       </c>
     </row>
     <row r="32">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>504</v>
+        <v>818</v>
       </c>
     </row>
     <row r="36">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1735</v>
+        <v>6557</v>
       </c>
     </row>
     <row r="38">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>852</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="39">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>311</v>
+        <v>454</v>
       </c>
     </row>
     <row r="40">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1015</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="42">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>162</v>
+        <v>289</v>
       </c>
     </row>
     <row r="43">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1024</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="44">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>305</v>
+        <v>784</v>
       </c>
     </row>
     <row r="45">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>285</v>
+        <v>626</v>
       </c>
     </row>
     <row r="46">
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>45</v>
+        <v>244</v>
       </c>
     </row>
     <row r="47">
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>68</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>97</v>
+        <v>526</v>
       </c>
     </row>
     <row r="49">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>139</v>
+        <v>293</v>
       </c>
     </row>
     <row r="51">
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>87</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>482</v>
+        <v>867</v>
       </c>
     </row>
     <row r="53">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>76</v>
+        <v>4828</v>
       </c>
     </row>
     <row r="55">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>29</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="56">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>12</v>
+        <v>399</v>
       </c>
     </row>
     <row r="57">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>65</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="58">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>360</v>
       </c>
     </row>
     <row r="59">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>173</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="60">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>358</v>
       </c>
     </row>
     <row r="61">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>30</v>
+        <v>252</v>
       </c>
     </row>
     <row r="62">
@@ -1235,11 +1235,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>114</v>
       </c>
     </row>
     <row r="63">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64">
@@ -1261,11 +1261,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>417</v>
       </c>
     </row>
     <row r="65">
@@ -1274,24 +1274,414 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>292</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B75" t="inlineStr">
         <is>
           <t>HUANUCO</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="C75" t="n">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LORETO</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>LORETO</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>282</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_total_departamentos.xlsx
+++ b/data/data_total_departamentos.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:C98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2669</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="4">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>895</v>
+        <v>901</v>
       </c>
     </row>
     <row r="10">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6285</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="21">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1186</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="27">
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="32">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6557</v>
+        <v>6581</v>
       </c>
     </row>
     <row r="38">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1918</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4828</v>
+        <v>4847</v>
       </c>
     </row>
     <row r="55">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2107</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="60">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>393</v>
+        <v>453</v>
       </c>
     </row>
     <row r="67">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1498</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="71">
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1903</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="74">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="76">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>51</v>
+        <v>147</v>
       </c>
     </row>
     <row r="80">
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>355</v>
+        <v>367</v>
       </c>
     </row>
     <row r="83">
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>171</v>
+        <v>289</v>
       </c>
     </row>
     <row r="86">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>634</v>
+        <v>727</v>
       </c>
     </row>
     <row r="87">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>148</v>
+        <v>186</v>
       </c>
     </row>
     <row r="91">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94">
@@ -1682,6 +1682,32 @@
       </c>
       <c r="C96" t="n">
         <v>282</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
